--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -57,6 +57,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4C4C9"/>
         <bgColor/>
       </patternFill>
@@ -75,85 +111,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFBEDEF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFEFA5AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,31 +189,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,6 +219,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF66C07B"/>
         <bgColor/>
       </patternFill>
@@ -237,169 +273,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1417,40 +1417,40 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="7">
         <v>18.7</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="11">
         <v>18.55</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="8">
         <v>38.58</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="1">
         <v>33.13</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>31.57</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="3">
         <v>29.4</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <v>22.29</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="12">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="5">
         <v>12.35</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="9">
         <v>14.34</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="6">
         <v>9.07</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="10">
         <v>1.45</v>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,40 +1479,40 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="25">
         <v>5.98</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="19">
         <v>23.88</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="20">
         <v>19.01</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="26">
         <v>17.61</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="14">
         <v>15.67</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="21">
         <v>9.32</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="22">
         <v>4.93</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="23">
         <v>0.43</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="24">
         <v>2.21</v>
       </c>
       <c r="R3" s="17">
         <v>-2.5</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="16">
         <v>3.1</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="15">
         <v>-9.32</v>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>920116</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -1877.24万</v>
       </c>
       <c r="E4">
@@ -1541,40 +1541,40 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="31">
         <v>-13.88</v>
       </c>
       <c r="J4" s="33">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="38">
         <v>-15</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="34">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="30">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="39">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="35">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="36">
         <v>-12.76</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="27">
         <v>-12.22</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="28">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="32">
         <v>-14.14</v>
       </c>
-      <c r="T4" s="36">
+      <c r="T4" s="37">
         <v>-25.01</v>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="50">
+      <c r="I6" s="45">
         <v>66.67</v>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="50">
         <v>66.67</v>
       </c>
-      <c r="K6" s="40">
+      <c r="K6" s="51">
         <v>66.67</v>
       </c>
       <c r="L6" s="43">
@@ -1652,25 +1652,25 @@
       <c r="M6" s="46">
         <v>66.67</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="40">
         <v>66.67</v>
       </c>
-      <c r="O6" s="49">
+      <c r="O6" s="41">
         <v>66.67</v>
       </c>
       <c r="P6" s="47">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="44">
         <v>66.67</v>
       </c>
-      <c r="R6" s="41">
+      <c r="R6" s="48">
         <v>33.33</v>
       </c>
       <c r="S6" s="42">
         <v>66.67</v>
       </c>
-      <c r="T6" s="48">
+      <c r="T6" s="49">
         <v>33.33</v>
       </c>
     </row>
@@ -1685,40 +1685,40 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="53">
+      <c r="I7" s="61">
         <v>3.6</v>
       </c>
-      <c r="J7" s="55">
+      <c r="J7" s="57">
         <v>9.74</v>
       </c>
-      <c r="K7" s="60">
+      <c r="K7" s="58">
         <v>14.2</v>
       </c>
-      <c r="L7" s="61">
+      <c r="L7" s="62">
         <v>10.18</v>
       </c>
-      <c r="M7" s="56">
+      <c r="M7" s="59">
         <v>8.84</v>
       </c>
-      <c r="N7" s="62">
+      <c r="N7" s="53">
         <v>7.62</v>
       </c>
-      <c r="O7" s="57">
+      <c r="O7" s="60">
         <v>7.89</v>
       </c>
       <c r="P7" s="63">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="58">
+      <c r="Q7" s="54">
         <v>0.78</v>
       </c>
       <c r="R7" s="52">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="55">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="54">
+      <c r="T7" s="56">
         <v>-10.96</v>
       </c>
     </row>

--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -51,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF4C4C9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,18 +93,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -123,72 +111,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE9818B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -243,6 +243,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF66C07B"/>
         <bgColor/>
       </patternFill>
@@ -267,79 +273,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,54 +375,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB8E1C1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB1212F"/>
         <bgColor/>
       </patternFill>
@@ -411,7 +393,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>920284</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="11" t="str">
         <v>净买: 5835.53万</v>
       </c>
       <c r="E2">
@@ -1417,40 +1417,40 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="10">
         <v>18.7</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="7">
         <v>18.55</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="12">
         <v>38.58</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="8">
         <v>33.13</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="13">
         <v>31.57</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="9">
         <v>29.4</v>
       </c>
       <c r="O2" s="4">
         <v>22.29</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="5">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="1">
         <v>12.35</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="2">
         <v>14.34</v>
       </c>
       <c r="S2" s="6">
         <v>9.07</v>
       </c>
-      <c r="T2" s="10">
+      <c r="T2" s="3">
         <v>1.45</v>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,40 +1479,40 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="21">
         <v>5.98</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="15">
         <v>23.88</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="26">
         <v>19.01</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="14">
         <v>17.61</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="16">
         <v>15.67</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="22">
         <v>9.32</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="23">
         <v>4.93</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="24">
         <v>0.43</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="18">
         <v>2.21</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="19">
         <v>-2.5</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="25">
         <v>3.1</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="20">
         <v>-9.32</v>
       </c>
     </row>
@@ -1541,40 +1541,40 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="30">
         <v>-13.88</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="35">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="31">
         <v>-15</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="38">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="32">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="33">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="36">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="34">
         <v>-12.76</v>
       </c>
       <c r="Q4" s="27">
         <v>-12.22</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="37">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="28">
         <v>-14.14</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="39">
         <v>-25.01</v>
       </c>
     </row>
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="45">
+      <c r="I6" s="47">
         <v>66.67</v>
       </c>
-      <c r="J6" s="50">
+      <c r="J6" s="48">
         <v>66.67</v>
       </c>
-      <c r="K6" s="51">
+      <c r="K6" s="49">
         <v>66.67</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="50">
         <v>66.67</v>
       </c>
-      <c r="M6" s="46">
+      <c r="M6" s="51">
         <v>66.67</v>
       </c>
       <c r="N6" s="40">
         <v>66.67</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="44">
         <v>66.67</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="41">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="44">
+      <c r="Q6" s="45">
         <v>66.67</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="46">
         <v>33.33</v>
       </c>
       <c r="S6" s="42">
         <v>66.67</v>
       </c>
-      <c r="T6" s="49">
+      <c r="T6" s="43">
         <v>33.33</v>
       </c>
     </row>
@@ -1685,40 +1685,40 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="61">
+      <c r="I7" s="58">
         <v>3.6</v>
       </c>
-      <c r="J7" s="57">
+      <c r="J7" s="60">
         <v>9.74</v>
       </c>
-      <c r="K7" s="58">
+      <c r="K7" s="61">
         <v>14.2</v>
       </c>
       <c r="L7" s="62">
         <v>10.18</v>
       </c>
-      <c r="M7" s="59">
+      <c r="M7" s="53">
         <v>8.84</v>
       </c>
-      <c r="N7" s="53">
+      <c r="N7" s="59">
         <v>7.62</v>
       </c>
-      <c r="O7" s="60">
+      <c r="O7" s="63">
         <v>7.89</v>
       </c>
-      <c r="P7" s="63">
+      <c r="P7" s="54">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="54">
+      <c r="Q7" s="55">
         <v>0.78</v>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="56">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="55">
+      <c r="S7" s="57">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="56">
+      <c r="T7" s="52">
         <v>-10.96</v>
       </c>
     </row>

--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -51,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,25 +75,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,19 +177,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,49 +195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,12 +213,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -249,6 +249,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF66C07B"/>
         <bgColor/>
       </patternFill>
@@ -267,6 +273,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -291,12 +333,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
@@ -309,37 +345,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,49 +399,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>920284</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="3" t="str">
         <v>净买: 5835.53万</v>
       </c>
       <c r="E2">
@@ -1417,31 +1417,31 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="8">
         <v>18.7</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="9">
         <v>18.55</v>
       </c>
       <c r="K2" s="12">
         <v>38.58</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="13">
         <v>33.13</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="10">
         <v>31.57</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="1">
         <v>29.4</v>
       </c>
       <c r="O2" s="4">
         <v>22.29</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="11">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="5">
         <v>12.35</v>
       </c>
       <c r="R2" s="2">
@@ -1450,8 +1450,8 @@
       <c r="S2" s="6">
         <v>9.07</v>
       </c>
-      <c r="T2" s="3">
-        <v>1.45</v>
+      <c r="T2" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="20" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="16">
         <v>5.98</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="21">
         <v>23.88</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="22">
         <v>19.01</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="23">
         <v>17.61</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="17">
         <v>15.67</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="18">
         <v>9.32</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="24">
         <v>4.93</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="25">
         <v>0.43</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="26">
         <v>2.21</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="14">
         <v>-2.5</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="15">
         <v>3.1</v>
       </c>
-      <c r="T3" s="20">
-        <v>-9.32</v>
+      <c r="T3" s="19">
+        <v>-10.8</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>920116</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -1877.24万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="28">
         <v>-13.88</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="29">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="33">
         <v>-15</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="34">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="30">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="35">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="37">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="31">
         <v>-12.76</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="36">
         <v>-12.22</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="32">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="38">
         <v>-14.14</v>
       </c>
       <c r="T4" s="39">
-        <v>-25.01</v>
+        <v>-20.13</v>
       </c>
     </row>
     <row r="5">
@@ -1637,10 +1637,10 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="47">
+      <c r="I6" s="48">
         <v>66.67</v>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="47">
         <v>66.67</v>
       </c>
       <c r="K6" s="49">
@@ -1649,29 +1649,29 @@
       <c r="L6" s="50">
         <v>66.67</v>
       </c>
-      <c r="M6" s="51">
+      <c r="M6" s="43">
         <v>66.67</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="44">
         <v>66.67</v>
       </c>
-      <c r="O6" s="44">
+      <c r="O6" s="51">
         <v>66.67</v>
       </c>
-      <c r="P6" s="41">
+      <c r="P6" s="40">
         <v>66.67</v>
       </c>
       <c r="Q6" s="45">
         <v>66.67</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="41">
         <v>33.33</v>
       </c>
       <c r="S6" s="42">
         <v>66.67</v>
       </c>
-      <c r="T6" s="43">
-        <v>33.33</v>
+      <c r="T6" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="58">
+      <c r="I7" s="61">
         <v>3.6</v>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="54">
         <v>9.74</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="55">
         <v>14.2</v>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="60">
         <v>10.18</v>
       </c>
-      <c r="M7" s="53">
+      <c r="M7" s="62">
         <v>8.84</v>
       </c>
-      <c r="N7" s="59">
+      <c r="N7" s="63">
         <v>7.62</v>
       </c>
-      <c r="O7" s="63">
+      <c r="O7" s="56">
         <v>7.89</v>
       </c>
-      <c r="P7" s="54">
+      <c r="P7" s="57">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="55">
+      <c r="Q7" s="52">
         <v>0.78</v>
       </c>
-      <c r="R7" s="56">
+      <c r="R7" s="53">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="57">
+      <c r="S7" s="58">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="52">
-        <v>-10.96</v>
+      <c r="T7" s="59">
+        <v>-10.38</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -45,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB0212F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,37 +69,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,19 +123,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE9818B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,49 +183,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,6 +249,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -231,121 +273,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,18 +405,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE15562"/>
         <bgColor/>
       </patternFill>
@@ -382,36 +412,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="12">
         <v>18.7</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="4">
         <v>18.55</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="1">
         <v>38.58</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="5">
         <v>33.13</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="6">
         <v>31.57</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="13">
         <v>29.4</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="7">
         <v>22.29</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="8">
         <v>12.35</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="10">
         <v>14.34</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="2">
         <v>9.07</v>
       </c>
-      <c r="T2" s="7">
-        <v>-0.21</v>
+      <c r="T2" s="11">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="23" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,28 +1479,28 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <v>5.98</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="19">
         <v>23.88</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="16">
         <v>19.01</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="17">
         <v>17.61</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="20">
         <v>15.67</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="24">
         <v>9.32</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="25">
         <v>4.93</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="21">
         <v>0.43</v>
       </c>
       <c r="Q3" s="26">
@@ -1509,11 +1509,11 @@
       <c r="R3" s="14">
         <v>-2.5</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="22">
         <v>3.1</v>
       </c>
-      <c r="T3" s="19">
-        <v>-10.8</v>
+      <c r="T3" s="18">
+        <v>-11.39</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>920116</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="33" t="str">
         <v>净卖: -1877.24万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="35">
         <v>-13.88</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="34">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="38">
         <v>-15</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="39">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="27">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="28">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="36">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="29">
         <v>-12.76</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="32">
         <v>-12.22</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="30">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="31">
         <v>-14.14</v>
       </c>
-      <c r="T4" s="39">
-        <v>-20.13</v>
+      <c r="T4" s="37">
+        <v>-22.63</v>
       </c>
     </row>
     <row r="5">
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="48">
+      <c r="I6" s="49">
         <v>66.67</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="51">
         <v>66.67</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="46">
         <v>66.67</v>
       </c>
-      <c r="L6" s="50">
+      <c r="L6" s="40">
         <v>66.67</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="47">
         <v>66.67</v>
       </c>
       <c r="N6" s="44">
         <v>66.67</v>
       </c>
-      <c r="O6" s="51">
+      <c r="O6" s="45">
         <v>66.67</v>
       </c>
-      <c r="P6" s="40">
+      <c r="P6" s="41">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="48">
         <v>66.67</v>
       </c>
-      <c r="R6" s="41">
+      <c r="R6" s="42">
         <v>33.33</v>
       </c>
-      <c r="S6" s="42">
+      <c r="S6" s="43">
         <v>66.67</v>
       </c>
-      <c r="T6" s="46">
+      <c r="T6" s="50">
         <v>0</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="61">
+      <c r="I7" s="52">
         <v>3.6</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="59">
         <v>9.74</v>
       </c>
-      <c r="K7" s="55">
+      <c r="K7" s="53">
         <v>14.2</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="54">
         <v>10.18</v>
       </c>
-      <c r="M7" s="62">
+      <c r="M7" s="58">
         <v>8.84</v>
       </c>
-      <c r="N7" s="63">
+      <c r="N7" s="61">
         <v>7.62</v>
       </c>
-      <c r="O7" s="56">
+      <c r="O7" s="55">
         <v>7.89</v>
       </c>
-      <c r="P7" s="57">
+      <c r="P7" s="62">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="52">
+      <c r="Q7" s="56">
         <v>0.78</v>
       </c>
-      <c r="R7" s="53">
+      <c r="R7" s="60">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="58">
+      <c r="S7" s="63">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="59">
-        <v>-10.38</v>
+      <c r="T7" s="57">
+        <v>-11.63</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -45,90 +45,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0212F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD1303F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -153,7 +183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,36 +195,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -219,6 +219,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -231,6 +237,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -249,7 +273,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,85 +285,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,55 +393,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>920284</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 5835.53万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="6">
         <v>18.7</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="7">
         <v>18.55</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="3">
         <v>38.58</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>33.13</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="8">
         <v>31.57</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="5">
         <v>29.4</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="11">
         <v>22.29</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="12">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="1">
         <v>12.35</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="9">
         <v>14.34</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="10">
         <v>9.07</v>
       </c>
-      <c r="T2" s="11">
-        <v>-0.87</v>
+      <c r="T2" s="13">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="16">
         <v>5.98</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="21">
         <v>23.88</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="19">
         <v>19.01</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="22">
         <v>17.61</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="24">
         <v>15.67</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="25">
         <v>9.32</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="17">
         <v>4.93</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="26">
         <v>0.43</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="18">
         <v>2.21</v>
       </c>
       <c r="R3" s="14">
         <v>-2.5</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="20">
         <v>3.1</v>
       </c>
-      <c r="T3" s="18">
-        <v>-11.39</v>
+      <c r="T3" s="23">
+        <v>-12.04</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>920116</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="37" t="str">
         <v>净卖: -1877.24万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="33">
         <v>-13.88</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="30">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="27">
         <v>-15</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="34">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="35">
         <v>-20.71</v>
       </c>
       <c r="N4" s="28">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="31">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="32">
         <v>-12.76</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="38">
         <v>-12.22</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="36">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="29">
         <v>-14.14</v>
       </c>
-      <c r="T4" s="37">
-        <v>-22.63</v>
+      <c r="T4" s="39">
+        <v>-27.85</v>
       </c>
     </row>
     <row r="5">
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="49">
+      <c r="I6" s="44">
         <v>66.67</v>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="45">
         <v>66.67</v>
       </c>
-      <c r="K6" s="46">
+      <c r="K6" s="42">
         <v>66.67</v>
       </c>
-      <c r="L6" s="40">
+      <c r="L6" s="49">
         <v>66.67</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="50">
         <v>66.67</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="51">
         <v>66.67</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="46">
         <v>66.67</v>
       </c>
-      <c r="P6" s="41">
+      <c r="P6" s="43">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="48">
+      <c r="Q6" s="40">
         <v>66.67</v>
       </c>
-      <c r="R6" s="42">
+      <c r="R6" s="47">
         <v>33.33</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="48">
         <v>66.67</v>
       </c>
-      <c r="T6" s="50">
+      <c r="T6" s="41">
         <v>0</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="52">
+      <c r="I7" s="57">
         <v>3.6</v>
       </c>
-      <c r="J7" s="59">
+      <c r="J7" s="58">
         <v>9.74</v>
       </c>
-      <c r="K7" s="53">
+      <c r="K7" s="61">
         <v>14.2</v>
       </c>
-      <c r="L7" s="54">
+      <c r="L7" s="52">
         <v>10.18</v>
       </c>
-      <c r="M7" s="58">
+      <c r="M7" s="55">
         <v>8.84</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="56">
         <v>7.62</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="59">
         <v>7.89</v>
       </c>
       <c r="P7" s="62">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="56">
+      <c r="Q7" s="63">
         <v>0.78</v>
       </c>
       <c r="R7" s="60">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="63">
+      <c r="S7" s="53">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="57">
-        <v>-11.63</v>
+      <c r="T7" s="54">
+        <v>-13.83</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -45,6 +45,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -75,19 +87,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF8D7DA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,7 +111,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBAE2C3"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,49 +129,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,30 +207,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -219,12 +237,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -255,126 +267,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB1212F"/>
         <bgColor/>
       </patternFill>
@@ -387,31 +405,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>920284</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 5835.53万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>18.7</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="11">
         <v>18.55</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="12">
         <v>38.58</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="6">
         <v>33.13</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="1">
         <v>31.57</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="2">
         <v>29.4</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="7">
         <v>22.29</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="3">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="8">
         <v>12.35</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="13">
         <v>14.34</v>
       </c>
       <c r="S2" s="10">
         <v>9.07</v>
       </c>
-      <c r="T2" s="13">
-        <v>-1.6</v>
+      <c r="T2" s="9">
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="24">
         <v>5.98</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="16">
         <v>23.88</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="17">
         <v>19.01</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="14">
         <v>17.61</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="25">
         <v>15.67</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="19">
         <v>9.32</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="20">
         <v>4.93</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="21">
         <v>0.43</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="22">
         <v>2.21</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="15">
         <v>-2.5</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="23">
         <v>3.1</v>
       </c>
-      <c r="T3" s="23">
-        <v>-12.04</v>
+      <c r="T3" s="18">
+        <v>-9.72</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>920116</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -1877.24万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="32">
         <v>-13.88</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="33">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="29">
         <v>-15</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="28">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="38">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="34">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="30">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="35">
         <v>-12.76</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="31">
         <v>-12.22</v>
       </c>
       <c r="R4" s="36">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="37">
         <v>-14.14</v>
       </c>
       <c r="T4" s="39">
-        <v>-27.85</v>
+        <v>-25.9</v>
       </c>
     </row>
     <row r="5">
@@ -1637,41 +1637,41 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="44">
+      <c r="I6" s="48">
         <v>66.67</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="49">
         <v>66.67</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="50">
         <v>66.67</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="51">
         <v>66.67</v>
       </c>
-      <c r="M6" s="50">
+      <c r="M6" s="44">
         <v>66.67</v>
       </c>
-      <c r="N6" s="51">
+      <c r="N6" s="43">
         <v>66.67</v>
       </c>
-      <c r="O6" s="46">
+      <c r="O6" s="45">
         <v>66.67</v>
       </c>
-      <c r="P6" s="43">
+      <c r="P6" s="40">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="40">
+      <c r="Q6" s="41">
         <v>66.67</v>
       </c>
-      <c r="R6" s="47">
+      <c r="R6" s="42">
         <v>33.33</v>
       </c>
-      <c r="S6" s="48">
+      <c r="S6" s="46">
         <v>66.67</v>
       </c>
-      <c r="T6" s="41">
-        <v>0</v>
+      <c r="T6" s="47">
+        <v>33.33</v>
       </c>
     </row>
     <row r="7">
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="57">
+      <c r="I7" s="60">
         <v>3.6</v>
       </c>
-      <c r="J7" s="58">
+      <c r="J7" s="53">
         <v>9.74</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="56">
         <v>14.2</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7" s="63">
         <v>10.18</v>
       </c>
-      <c r="M7" s="55">
+      <c r="M7" s="54">
         <v>8.84</v>
       </c>
-      <c r="N7" s="56">
+      <c r="N7" s="55">
         <v>7.62</v>
       </c>
-      <c r="O7" s="59">
+      <c r="O7" s="61">
         <v>7.89</v>
       </c>
-      <c r="P7" s="62">
+      <c r="P7" s="57">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="63">
+      <c r="Q7" s="62">
         <v>0.78</v>
       </c>
-      <c r="R7" s="60">
+      <c r="R7" s="52">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="53">
+      <c r="S7" s="58">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="54">
-        <v>-13.83</v>
+      <c r="T7" s="59">
+        <v>-11.54</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小棉袄/index.xlsx
+++ b/youzi/小棉袄/index.xlsx
@@ -57,6 +57,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -87,37 +99,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,61 +165,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE9818B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD1303F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,145 +273,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -358,54 +406,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>920284</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="6" t="str">
         <v>净买: 5835.53万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>9.5</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="10">
         <v>18.7</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="1">
         <v>18.55</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="11">
         <v>38.58</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="2">
         <v>33.13</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="7">
         <v>31.57</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="3">
         <v>29.4</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="8">
         <v>22.29</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="9">
         <v>17.38</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="12">
         <v>12.35</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="4">
         <v>14.34</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="5">
         <v>9.07</v>
       </c>
-      <c r="T2" s="9">
-        <v>0.99</v>
+      <c r="T2" s="13">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>920284</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 474.62万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>-5.76</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="26">
         <v>5.98</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="14">
         <v>23.88</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="18">
         <v>19.01</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="21">
         <v>17.61</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="15">
         <v>15.67</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="22">
         <v>9.32</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="19">
         <v>4.93</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="16">
         <v>0.43</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="17">
         <v>2.21</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="20">
         <v>-2.5</v>
       </c>
       <c r="S3" s="23">
         <v>3.1</v>
       </c>
-      <c r="T3" s="18">
-        <v>-9.72</v>
+      <c r="T3" s="24">
+        <v>-13.17</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>920116</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -1877.24万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-8.22</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="37">
         <v>-13.88</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="38">
         <v>-13.21</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="27">
         <v>-15</v>
       </c>
       <c r="L4" s="28">
         <v>-20.21</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="33">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="29">
         <v>-15.87</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="34">
         <v>-3.54</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="31">
         <v>-12.76</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="32">
         <v>-12.22</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="30">
         <v>-15.82</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="35">
         <v>-14.14</v>
       </c>
-      <c r="T4" s="39">
-        <v>-25.9</v>
+      <c r="T4" s="36">
+        <v>-28.88</v>
       </c>
     </row>
     <row r="5">
@@ -1637,41 +1637,41 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="48">
+      <c r="I6" s="47">
         <v>66.67</v>
       </c>
-      <c r="J6" s="49">
+      <c r="J6" s="48">
         <v>66.67</v>
       </c>
       <c r="K6" s="50">
         <v>66.67</v>
       </c>
-      <c r="L6" s="51">
+      <c r="L6" s="44">
         <v>66.67</v>
       </c>
-      <c r="M6" s="44">
+      <c r="M6" s="40">
         <v>66.67</v>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="41">
         <v>66.67</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="42">
         <v>66.67</v>
       </c>
-      <c r="P6" s="40">
+      <c r="P6" s="45">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="41">
+      <c r="Q6" s="51">
         <v>66.67</v>
       </c>
-      <c r="R6" s="42">
+      <c r="R6" s="49">
         <v>33.33</v>
       </c>
-      <c r="S6" s="46">
+      <c r="S6" s="43">
         <v>66.67</v>
       </c>
-      <c r="T6" s="47">
-        <v>33.33</v>
+      <c r="T6" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="60">
+      <c r="I7" s="59">
         <v>3.6</v>
       </c>
-      <c r="J7" s="53">
+      <c r="J7" s="57">
         <v>9.74</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="61">
         <v>14.2</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="53">
         <v>10.18</v>
       </c>
-      <c r="M7" s="54">
+      <c r="M7" s="62">
         <v>8.84</v>
       </c>
-      <c r="N7" s="55">
+      <c r="N7" s="63">
         <v>7.62</v>
       </c>
-      <c r="O7" s="61">
+      <c r="O7" s="58">
         <v>7.89</v>
       </c>
-      <c r="P7" s="57">
+      <c r="P7" s="54">
         <v>1.68</v>
       </c>
-      <c r="Q7" s="62">
+      <c r="Q7" s="55">
         <v>0.78</v>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="60">
         <v>-1.33</v>
       </c>
-      <c r="S7" s="58">
+      <c r="S7" s="52">
         <v>-0.66</v>
       </c>
-      <c r="T7" s="59">
-        <v>-11.54</v>
+      <c r="T7" s="56">
+        <v>-14.97</v>
       </c>
     </row>
   </sheetData>
